--- a/inbody.xlsx
+++ b/inbody.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_BC2F0BE505820D34A8D42BD1E2FA7955F18D780B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7FC45A-E6B6-4137-AC12-D71792AD171B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF271C7-7A68-4797-ADDE-5B215A75323C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -94,10 +94,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,16 +131,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -412,33 +423,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R77"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -490,22 +501,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>43153</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>156.1</v>
       </c>
       <c r="C2" s="1">
         <v>73.2</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>43229</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="4">
         <v>156.69999999999999</v>
       </c>
       <c r="C3" s="1">
@@ -557,11 +568,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>43264</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>157</v>
       </c>
       <c r="C4" s="1">
@@ -613,11 +624,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>43305</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>158</v>
       </c>
       <c r="C5" s="1">
@@ -669,11 +680,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>43505</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>151</v>
       </c>
       <c r="C6" s="1">
@@ -725,11 +736,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>43519</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="4">
         <v>153.6</v>
       </c>
       <c r="C7" s="1">
@@ -781,11 +792,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>43586</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="4">
         <v>154.5</v>
       </c>
       <c r="C8" s="1">
@@ -837,11 +848,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>43617</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="4">
         <v>150</v>
       </c>
       <c r="C9" s="1">
@@ -893,11 +904,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>43659</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>149.80000000000001</v>
       </c>
       <c r="C10" s="1">
@@ -949,11 +960,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>43673</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="4">
         <v>147</v>
       </c>
       <c r="C11" s="1">
@@ -1005,11 +1016,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>43705</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="4">
         <v>149.4</v>
       </c>
       <c r="C12" s="1">
@@ -1061,11 +1072,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>43783</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="4">
         <v>147</v>
       </c>
       <c r="C13" s="1">
@@ -1117,11 +1128,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>43813</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>149.9</v>
       </c>
       <c r="C14" s="1">
@@ -1173,11 +1184,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>43827</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="4">
         <v>151</v>
       </c>
       <c r="C15" s="1">
@@ -1229,11 +1240,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>43847</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="4">
         <v>152.1</v>
       </c>
       <c r="C16" s="1">
@@ -1285,11 +1296,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>43887</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="4">
         <v>156</v>
       </c>
       <c r="C17" s="1">
@@ -1341,11 +1352,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>43902</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="4">
         <v>157.69999999999999</v>
       </c>
       <c r="C18" s="1">
@@ -1397,11 +1408,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>44241</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="4">
         <v>158</v>
       </c>
       <c r="C19" s="1">
@@ -1453,11 +1464,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>44337</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="4">
         <v>163.9</v>
       </c>
       <c r="C20" s="1">
@@ -1509,11 +1520,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>44358</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="4">
         <v>164</v>
       </c>
       <c r="C21" s="1">
@@ -1565,11 +1576,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>44408</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="4">
         <v>157</v>
       </c>
       <c r="C22" s="1">
@@ -1621,11 +1632,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>44485</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="4">
         <v>155.5</v>
       </c>
       <c r="C23" s="1">
@@ -1677,11 +1688,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45339</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="4">
         <v>164.5</v>
       </c>
       <c r="C24" s="1">
@@ -1733,11 +1744,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45641</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="4">
         <v>164</v>
       </c>
       <c r="C25" s="1">
@@ -1789,160 +1800,372 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="2"/>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="2"/>
-    </row>
-    <row r="30" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>45675</v>
+      </c>
+      <c r="B26" s="4">
+        <v>162.9</v>
+      </c>
+      <c r="C26" s="1">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="D26" s="1">
+        <v>28.7</v>
+      </c>
+      <c r="E26" s="1">
+        <v>24.1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="G26" s="1">
+        <v>7.76</v>
+      </c>
+      <c r="H26" s="1">
+        <v>7.98</v>
+      </c>
+      <c r="I26" s="1">
+        <v>61.6</v>
+      </c>
+      <c r="J26" s="1">
+        <v>19.86</v>
+      </c>
+      <c r="K26" s="1">
+        <v>20.11</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="M26" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="N26" s="1">
+        <v>15.4</v>
+      </c>
+      <c r="O26" s="1">
+        <v>4</v>
+      </c>
+      <c r="P26" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="R26" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>45715</v>
+      </c>
+      <c r="B27" s="4">
+        <v>158.1</v>
+      </c>
+      <c r="C27" s="1">
+        <v>75</v>
+      </c>
+      <c r="D27" s="1">
+        <v>27.6</v>
+      </c>
+      <c r="E27" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="F27" s="1">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="G27" s="1">
+        <v>7.56</v>
+      </c>
+      <c r="H27" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="I27" s="1">
+        <v>60.1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="K27" s="1">
+        <v>19.690000000000001</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M27" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N27" s="1">
+        <v>14.6</v>
+      </c>
+      <c r="O27" s="1">
+        <v>4</v>
+      </c>
+      <c r="P27" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="R27" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>45873</v>
+      </c>
+      <c r="B28" s="4">
+        <v>155.9</v>
+      </c>
+      <c r="C28" s="1">
+        <v>75.8</v>
+      </c>
+      <c r="D28" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="E28" s="1">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="G28" s="1">
+        <v>7.74</v>
+      </c>
+      <c r="H28" s="1">
+        <v>7.72</v>
+      </c>
+      <c r="I28" s="1">
+        <v>60.8</v>
+      </c>
+      <c r="J28" s="1">
+        <v>19.84</v>
+      </c>
+      <c r="K28" s="1">
+        <v>19.89</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="N28" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="O28" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="P28" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="R28" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B29" s="4">
+        <v>166.6</v>
+      </c>
+      <c r="C29" s="1">
+        <v>78.7</v>
+      </c>
+      <c r="D29" s="1">
+        <v>29.7</v>
+      </c>
+      <c r="E29" s="1">
+        <v>25</v>
+      </c>
+      <c r="F29" s="1">
+        <v>17.8</v>
+      </c>
+      <c r="G29" s="1">
+        <v>7.85</v>
+      </c>
+      <c r="H29" s="1">
+        <v>8.14</v>
+      </c>
+      <c r="I29" s="1">
+        <v>62.4</v>
+      </c>
+      <c r="J29" s="1">
+        <v>20.37</v>
+      </c>
+      <c r="K29" s="1">
+        <v>20.59</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="M29" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N29" s="1">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="O29" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="P29" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="R29" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
     </row>
   </sheetData>
